--- a/workbooks/professor_details.xlsx
+++ b/workbooks/professor_details.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Details</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:22Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:22Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/professor_details.xlsx
+++ b/workbooks/professor_details.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Details</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:44Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:44Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -85,7 +85,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,720 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="0">
+        <is>
+          <t>WHU-CS-001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t>Wuhan University</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="0">
+        <is>
+          <t>Sheng Wang</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="0">
+        <is>
+          <t>C502, School of Computer Science, Wuhan University, China</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr" s="0">
+        <is>
+          <t>Ph.D. from RMIT University; M.E. and B.E. from Nanjing University of Aeronautics and Astronautics</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr" s="0">
+        <is>
+          <t>Professor at the School of Computer Science with concurrent affiliation to the School of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr" s="0">
+        <is>
+          <t>Always looking for highly self-motivated Postdocs, Ph.D, and master students</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr" s="0">
+        <is>
+          <t>Main research focuses on multi-model database theory and systems, with applications in scientific discovery, public transportation, and data markets</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr" s="0">
+        <is>
+          <t>https://sheng.whu.edu.cn/</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr" s="0">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr" s="0">
+        <is>
+          <t>Verified official source</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr" s="0">
+        <is>
+          <t>Official WHU personal page on whu.edu.cn domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t>WHU-CS-002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t>Wuhan University</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="0">
+        <is>
+          <t>Hao Wang</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="0">
+        <is>
+          <t>E203, School of Computer Science</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr" s="0">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr" s="0">
+        <is>
+          <t>Ph.D. in Philosophy, The University of Hong Kong, 2014; M.Eng., Nanjing University, 2008; B.Sc., Nanjing University, 2005</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr" s="0">
+        <is>
+          <t>Full professor at the School of Computer Science, Wuhan University</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr" s="0">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr" s="0">
+        <is>
+          <t>National outstanding youth fund winner (2022)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr" s="0">
+        <is>
+          <t>Published over 40 papers in TKDE, VLDB, VLDB Journal, SIGMOD, IJCAI, AAAI and related venues</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr" s="0">
+        <is>
+          <t>https://jszy.whu.edu.cn/wanghao6/en/index.htm</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr" s="0">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr" s="0">
+        <is>
+          <t>Verified official source</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr" s="0">
+        <is>
+          <t>Official Wuhan University faculty profile includes education and admission information</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="0">
+        <is>
+          <t>HUST-CS-001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="0">
+        <is>
+          <t>Jin Renchao</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="0">
+        <is>
+          <t>027-87792212</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr" s="0">
+        <is>
+          <t>Doctoral Degree in Computer Software and Theory, Huazhong University of Science and Technology; Master's and Bachelor's in same field from HUST</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr" s="0">
+        <is>
+          <t>Professor and doctoral supervisor in Medical Image Information Research Center</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr" s="0">
+        <is>
+          <t>Has taken charge of multiple NSFC and national projects</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr" s="0">
+        <is>
+          <t>Mainly engaged in AI, medical image processing and analysis, and computer vision research</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1446/1433.htm</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr" s="0">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr" s="0">
+        <is>
+          <t>Verified official source</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr" s="0">
+        <is>
+          <t>Official HUST profile includes phone and academic degree history</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="0">
+        <is>
+          <t>HUST-CS-002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="0">
+        <is>
+          <t>Chen Jincai</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="0">
+        <is>
+          <t>18986113859</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr" s="0">
+        <is>
+          <t>Doctor degree from Xi'an Jiaotong University in computer architecture, 2000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr" s="0">
+        <is>
+          <t>Professor; postdoctoral research in storage systems; visiting researcher at University of California Santa Cruz 2011-2012</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr" s="0">
+        <is>
+          <t>More than 30 invention patents including 2 US invention patents</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr" s="0">
+        <is>
+          <t>Published more than 100 papers; led 4 NSFC projects and participated in 973 and 863 projects</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1464/1187.htm</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr" s="0">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr" s="0">
+        <is>
+          <t>Verified official source</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr" s="0">
+        <is>
+          <t>Official HUST profile includes phone education and publication/project summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="0">
+        <is>
+          <t>TJU-CS-001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="0">
+        <is>
+          <t>Bo Wang</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="0">
+        <is>
+          <t>+86 13512828426</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr" s="0">
+        <is>
+          <t>Building 55, Room 516, No.135 Yaguan Road, Jinnan District, Tianjin, China</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr" s="0">
+        <is>
+          <t>http://cs.tju.edu.cn/faculty/wangbo/index.htm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor, School of Computer Science and Technology, Tianjin University</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr" s="0">
+        <is>
+          <t>Personalized recommendation; intelligent customer service; computational psychology</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr" s="0">
+        <is>
+          <t>Research interests include intelligent dialog systems, computational psychology, recommendation, and NLP</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr" s="0">
+        <is>
+          <t>https://tiei.tju.edu.cn/info/1614/3494.htm</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr" s="0">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr" s="0">
+        <is>
+          <t>Verified official source</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr" s="0">
+        <is>
+          <t>Official Tianjin University profile includes phone office website</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t>TJU-CS-002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="0">
+        <is>
+          <t>Kun Li</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin 300350, China</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr" s="0">
+        <is>
+          <t>Ph.D. 2011, Department of Automation, Tsinghua University; B.Eng. 2006, Beijing University of Posts and Telecommunications</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr" s="0">
+        <is>
+          <t>Professor since July 2022; Associate Professor 2014-2022; Assistant Professor 2011-2014; postdoc and visiting scholar at EPFL</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr" s="0">
+        <is>
+          <t>Research page centers on 3D vision and digital humans</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/likun/bio.html</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr" s="0">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr" s="0">
+        <is>
+          <t>Verified official source</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr" s="0">
+        <is>
+          <t>Official Tianjin University faculty profile includes education and professional experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t>SYSU-001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="0">
+        <is>
+          <t>Li Wenjun</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr" s="0">
+        <is>
+          <t>132 East Waihuan Road, Guangzhou Higher Education Mega Center, Guangzhou 510006, P. R. China</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr" s="0">
+        <is>
+          <t>Ph.D., Institute of Software, Chinese Academy of Sciences, 2001; Master's and undergraduate degrees from Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr" s="0">
+        <is>
+          <t>Full Professor since 2006 with earlier roles as associate professor assistant professor and teaching assistant at SYSU</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr" s="0">
+        <is>
+          <t>Long-term faculty member in computer science and software related schools at SYSU</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr" s="0">
+        <is>
+          <t>https://cse.sysu.edu.cn/en/teacher/LiWenjun</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr" s="0">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr" s="0">
+        <is>
+          <t>Verified official source</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr" s="0">
+        <is>
+          <t>Official SYSU faculty profile includes address employment history and education</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/workbooks/professor_details.xlsx
+++ b/workbooks/professor_details.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Details</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:44Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:44Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/professor_details.xlsx
+++ b/workbooks/professor_details.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Details</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:57:19Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:57:19Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
